--- a/artfynd/A 9585-2020 artfynd.xlsx
+++ b/artfynd/A 9585-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9585-2020 artfynd.xlsx
+++ b/artfynd/A 9585-2020 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122369535</v>
+        <v>122369532</v>
       </c>
       <c r="B3" t="n">
         <v>56584</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386908</v>
+        <v>386994</v>
       </c>
       <c r="R3" t="n">
-        <v>6648029</v>
+        <v>6647829</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,11 +871,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-04-24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122369532</v>
+        <v>122369535</v>
       </c>
       <c r="B4" t="n">
         <v>56584</v>
@@ -950,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386994</v>
+        <v>386908</v>
       </c>
       <c r="R4" t="n">
-        <v>6647829</v>
+        <v>6648029</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,6 +981,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 9585-2020 artfynd.xlsx
+++ b/artfynd/A 9585-2020 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122369532</v>
+        <v>122369535</v>
       </c>
       <c r="B3" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386994</v>
+        <v>386908</v>
       </c>
       <c r="R3" t="n">
-        <v>6647829</v>
+        <v>6648029</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,6 +871,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122369535</v>
+        <v>122369532</v>
       </c>
       <c r="B4" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386908</v>
+        <v>386994</v>
       </c>
       <c r="R4" t="n">
-        <v>6648029</v>
+        <v>6647829</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,11 +986,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-04-24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 9585-2020 artfynd.xlsx
+++ b/artfynd/A 9585-2020 artfynd.xlsx
@@ -805,11 +805,6 @@
       <c r="E3" t="n">
         <v>100138</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Tetrao urogallus</t>
@@ -919,11 +914,6 @@
       </c>
       <c r="E4" t="n">
         <v>100138</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 9585-2020 artfynd.xlsx
+++ b/artfynd/A 9585-2020 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122369535</v>
+        <v>122369532</v>
       </c>
       <c r="B3" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,6 +804,11 @@
       </c>
       <c r="E3" t="n">
         <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -830,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386908</v>
+        <v>386994</v>
       </c>
       <c r="R3" t="n">
-        <v>6648029</v>
+        <v>6647829</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,11 +871,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-04-24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122369532</v>
+        <v>122369535</v>
       </c>
       <c r="B4" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,6 +914,11 @@
       </c>
       <c r="E4" t="n">
         <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -940,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386994</v>
+        <v>386908</v>
       </c>
       <c r="R4" t="n">
-        <v>6647829</v>
+        <v>6648029</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,6 +981,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 9585-2020 artfynd.xlsx
+++ b/artfynd/A 9585-2020 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122369532</v>
+        <v>122369535</v>
       </c>
       <c r="B3" t="n">
         <v>56593</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386994</v>
+        <v>386908</v>
       </c>
       <c r="R3" t="n">
-        <v>6647829</v>
+        <v>6648029</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,6 +871,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122369535</v>
+        <v>122369532</v>
       </c>
       <c r="B4" t="n">
         <v>56593</v>
@@ -945,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386908</v>
+        <v>386994</v>
       </c>
       <c r="R4" t="n">
-        <v>6648029</v>
+        <v>6647829</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,11 +986,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-04-24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 9585-2020 artfynd.xlsx
+++ b/artfynd/A 9585-2020 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>122369535</v>
       </c>
       <c r="B3" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>122369532</v>
       </c>
       <c r="B4" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 9585-2020 artfynd.xlsx
+++ b/artfynd/A 9585-2020 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122369535</v>
+        <v>122369532</v>
       </c>
       <c r="B3" t="n">
         <v>56594</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386908</v>
+        <v>386994</v>
       </c>
       <c r="R3" t="n">
-        <v>6648029</v>
+        <v>6647829</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,11 +871,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-04-24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122369532</v>
+        <v>122369535</v>
       </c>
       <c r="B4" t="n">
         <v>56594</v>
@@ -950,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386994</v>
+        <v>386908</v>
       </c>
       <c r="R4" t="n">
-        <v>6647829</v>
+        <v>6648029</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,6 +981,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 9585-2020 artfynd.xlsx
+++ b/artfynd/A 9585-2020 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122369532</v>
+        <v>122369535</v>
       </c>
       <c r="B3" t="n">
         <v>56594</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386994</v>
+        <v>386908</v>
       </c>
       <c r="R3" t="n">
-        <v>6647829</v>
+        <v>6648029</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,6 +871,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122369535</v>
+        <v>122369532</v>
       </c>
       <c r="B4" t="n">
         <v>56594</v>
@@ -945,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386908</v>
+        <v>386994</v>
       </c>
       <c r="R4" t="n">
-        <v>6648029</v>
+        <v>6647829</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,11 +986,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-04-24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD4" t="b">
